--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656151e-05</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C31" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D36" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D67" t="n">
-        <v>3.069580937579263e-05</v>
+        <v>3.069580937579264e-05</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C68" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D68" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D71" t="n">
         <v>1.260532007533779e-05</v>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>6.727132866723797e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>1.462420188418218e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D75" t="n">
-        <v>1.488974146445568e-05</v>
+        <v>1.488974146445571e-05</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D92" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656151e-05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C97" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D108" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>1.92785536800617e-05</v>
+        <v>1.927855368006169e-05</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D172" t="n">
-        <v>3.069580937579263e-05</v>
+        <v>3.069580937579264e-05</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C179" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D179" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D188" t="n">
         <v>1.260532007533779e-05</v>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>6.727132866723797e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>1.462420188418218e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D225" t="n">
-        <v>1.488974146445568e-05</v>
+        <v>1.488974146445571e-05</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D227" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656151e-05</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8168,10 +8168,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0001596599792992578</v>
+        <v>0.0001596599792992579</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560655e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8328,10 +8328,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0003835999729223548</v>
+        <v>0.0003835999729223549</v>
       </c>
       <c r="D236" t="n">
-        <v>2.256470428955038e-05</v>
+        <v>2.256470428955027e-05</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D240" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8488,10 +8488,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C241" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D241" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.30563090409638e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747834e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.520351809408697e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8872,10 +8872,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C253" t="n">
-        <v>8.979401253524415e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D253" t="n">
-        <v>3.142790438733546e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192755e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440956e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9160,10 +9160,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C262" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100009e-05</v>
       </c>
       <c r="D262" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346959e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9192,7 +9192,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>4.256883574234244e-05</v>
+        <v>4.256883574234245e-05</v>
       </c>
       <c r="D263" t="n">
         <v>2.321936495036861e-05</v>
@@ -9227,7 +9227,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.832206526319646e-05</v>
+        <v>1.832206526319647e-05</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D267" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D271" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860084</v>
+        <v>0.0006768150688860083</v>
       </c>
       <c r="D272" t="n">
-        <v>5.73572092276277e-05</v>
+        <v>5.73572092276278e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9512,10 +9512,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0001318629153132403</v>
+        <v>0.0001318629153132404</v>
       </c>
       <c r="D273" t="n">
-        <v>4.615202035963416e-05</v>
+        <v>4.615202035963413e-05</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9544,10 +9544,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C274" t="n">
-        <v>5.966987640876849e-05</v>
+        <v>5.96698764087685e-05</v>
       </c>
       <c r="D274" t="n">
-        <v>1.491746910219212e-05</v>
+        <v>1.491746910219211e-05</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>6.076810889645114e-05</v>
+        <v>6.076810889645115e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.430724355858046e-05</v>
+        <v>2.430724355858045e-05</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D292" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>3.420241241015533e-05</v>
+        <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507766e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D322" t="n">
-        <v>3.069580937579263e-05</v>
+        <v>3.069580937579264e-05</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11112,10 +11112,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C323" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D323" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11208,7 +11208,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D326" t="n">
         <v>1.260532007533779e-05</v>
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>6.727132866723797e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>1.462420188418218e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D330" t="n">
-        <v>1.488974146445568e-05</v>
+        <v>1.488974146445571e-05</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11371,7 +11371,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D398" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656151e-05</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13708,10 +13708,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0001596599792992578</v>
+        <v>0.0001596599792992579</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560655e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0003835999729223548</v>
+        <v>0.0003835999729223549</v>
       </c>
       <c r="D413" t="n">
-        <v>2.256470428955038e-05</v>
+        <v>2.256470428955027e-05</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14215,7 +14215,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D423" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
@@ -14240,10 +14240,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C424" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D424" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.30563090409638e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747834e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.520351809408697e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C448" t="n">
-        <v>8.979401253524415e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>3.142790438733546e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192755e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440956e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C463" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100009e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346959e-05</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15528,7 +15528,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>4.256883574234244e-05</v>
+        <v>4.256883574234245e-05</v>
       </c>
       <c r="D470" t="n">
         <v>2.321936495036861e-05</v>
@@ -15559,7 +15559,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.832206526319646e-05</v>
+        <v>1.832206526319647e-05</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -17488,10 +17488,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C540" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D540" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D547" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860084</v>
+        <v>0.0006768150688860083</v>
       </c>
       <c r="D548" t="n">
-        <v>5.73572092276277e-05</v>
+        <v>5.73572092276278e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17740,10 +17740,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C549" t="n">
-        <v>0.0001318629153132403</v>
+        <v>0.0001318629153132404</v>
       </c>
       <c r="D549" t="n">
-        <v>4.615202035963416e-05</v>
+        <v>4.615202035963413e-05</v>
       </c>
       <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr"/>
@@ -17936,10 +17936,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C556" t="n">
-        <v>5.966987640876849e-05</v>
+        <v>5.96698764087685e-05</v>
       </c>
       <c r="D556" t="n">
-        <v>1.491746910219212e-05</v>
+        <v>1.491746910219211e-05</v>
       </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>6.076810889645114e-05</v>
+        <v>6.076810889645115e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.430724355858046e-05</v>
+        <v>2.430724355858045e-05</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18328,7 +18328,7 @@
         <v>3.023137075753097e-05</v>
       </c>
       <c r="C570" t="n">
-        <v>1.343616478112487e-05</v>
+        <v>1.343616478112488e-05</v>
       </c>
       <c r="D570" t="n">
         <v>1.679520597640609e-05</v>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18779,7 +18779,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D586" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>3.420241241015533e-05</v>
+        <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507766e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>1.92785536800617e-05</v>
+        <v>1.927855368006169e-05</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D694" t="n">
-        <v>3.069580937579263e-05</v>
+        <v>3.069580937579264e-05</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21996,10 +21996,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C701" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D701" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22248,7 +22248,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D710" t="n">
         <v>1.260532007533779e-05</v>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>6.727132866723797e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>1.462420188418218e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D747" t="n">
-        <v>1.488974146445568e-05</v>
+        <v>1.488974146445571e-05</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23315,7 +23315,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -480,10 +480,10 @@
         <v>0.0004249893752656184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004462570396636331</v>
+        <v>0.0004249893752656184</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.126766439801474e-05</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -516,10 +516,10 @@
         <v>0.0002690341673392521</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000217847634944532</v>
+        <v>0.0002105484787872408</v>
       </c>
       <c r="D3" t="n">
-        <v>5.118653239472005e-05</v>
+        <v>5.84856885520113e-05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -552,10 +552,10 @@
         <v>0.0001252114110578495</v>
       </c>
       <c r="C4" t="n">
-        <v>8.199570935088323e-05</v>
+        <v>8.035956232070945e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>4.321570170696631e-05</v>
+        <v>4.485184873714008e-05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>0.005405405405405406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006327485380116959</v>
+        <v>0.005405405405405405</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0009220799747115529</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>0.003996003996003996</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004602377679300756</v>
+        <v>0.003996003996003996</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0006063736832967598</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         <v>0.0008048289738430583</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008656291139925339</v>
+        <v>0.0008048289738430583</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.080014014947554e-05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>0.0003755692221022487</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003418244624823695</v>
+        <v>0.0003286230693394675</v>
       </c>
       <c r="D8" t="n">
-        <v>3.37447596198792e-05</v>
+        <v>4.694615276278123e-05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -732,10 +732,10 @@
         <v>9.69976831864852e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>6.44806895223694e-05</v>
+        <v>6.360503815507227e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.25169936641158e-05</v>
+        <v>3.339264503141293e-05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
         <v>0.0001527628979121734</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001299145972413765</v>
+        <v>0.0001286424403470934</v>
       </c>
       <c r="D10" t="n">
-        <v>2.284830067079694e-05</v>
+        <v>2.412045756508002e-05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>0.02795248078266946</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03039061989679274</v>
+        <v>0.02795248078266947</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.002438139114123279</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         <v>0.004048582995951417</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00409087588574768</v>
+        <v>0.002699055330634278</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.229288979626291e-05</v>
+        <v>0.001349527665317139</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -876,10 +876,10 @@
         <v>0.006451612903225806</v>
       </c>
       <c r="C13" t="n">
-        <v>0.009157127991675337</v>
+        <v>0.006451612903225806</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00270551508844953</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>0.1396825396825397</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1440065037003813</v>
+        <v>0.1396825396825397</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.004323964017841575</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         <v>0.1756214915797915</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1781874157022789</v>
+        <v>0.1756214915797915</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.002565924122487434</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         <v>0.1184210526315789</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1231769260768921</v>
+        <v>0.118421052631579</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.004755873445313155</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>0.0003320880033208801</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0003602403830763987</v>
+        <v>0.00033208800332088</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.815237975551863e-05</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         <v>0.0002788551727634547</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0002520857868433707</v>
+        <v>0.0002450545457618239</v>
       </c>
       <c r="D18" t="n">
-        <v>2.676938592008408e-05</v>
+        <v>3.380062700163085e-05</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>8.177577330764418e-05</v>
       </c>
       <c r="C19" t="n">
-        <v>6.040646490025689e-05</v>
+        <v>5.947328967828667e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>2.136930840738729e-05</v>
+        <v>2.230248362935751e-05</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         <v>5.677872792631042e-05</v>
       </c>
       <c r="C20" t="n">
-        <v>3.941691792627584e-05</v>
+        <v>3.913128546272745e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>1.736181000003458e-05</v>
+        <v>1.764744246358297e-05</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>4.816666614025502e-05</v>
       </c>
       <c r="C21" t="n">
-        <v>3.352028040587719e-05</v>
+        <v>3.316393406378214e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>1.464638573437783e-05</v>
+        <v>1.500273207647288e-05</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>4.221507380305824e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>2.462374649261735e-05</v>
+        <v>2.444030588598108e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.759132731044088e-05</v>
+        <v>1.777476791707716e-05</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>0.306184012066365</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3068240288139953</v>
+        <v>0.306184012066365</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.000640016747630312</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>0.6994482310938007</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7003211384957719</v>
+        <v>0.6994482310938007</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0008729074019712124</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>0.09090909090909091</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0935655253837072</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.00265643447461629</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         <v>9.995502024089161e-05</v>
       </c>
       <c r="C26" t="n">
-        <v>6.189937046625438e-05</v>
+        <v>6.068697657482704e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>3.805564977463723e-05</v>
+        <v>3.926804366606457e-05</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         <v>4.877771833826308e-05</v>
       </c>
       <c r="C27" t="n">
-        <v>2.177846034081472e-05</v>
+        <v>2.159013762513284e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>2.699925799744836e-05</v>
+        <v>2.718758071313024e-05</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
         <v>0.0001522986715402242</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001435413908894575</v>
+        <v>0.0001384533377638401</v>
       </c>
       <c r="D28" t="n">
-        <v>8.757280650766649e-06</v>
+        <v>1.384533377638401e-05</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.981525720656151e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C31" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D36" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482712e-06</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>3.78159602260134e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D71" t="n">
         <v>1.260532007533779e-05</v>
@@ -3000,7 +3000,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D72" t="n">
         <v>1.492001380598611e-05</v>
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D92" t="n">
-        <v>3.981525720656151e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C97" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D108" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482712e-06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>3.78159602260134e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D188" t="n">
         <v>1.260532007533779e-05</v>
@@ -6824,7 +6824,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D189" t="n">
         <v>1.492001380598611e-05</v>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D227" t="n">
-        <v>3.981525720656151e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8424,7 +8424,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>4.862394242925216e-05</v>
+        <v>4.862394242925217e-05</v>
       </c>
       <c r="D239" t="n">
         <v>1.736569372473291e-05</v>
@@ -8488,10 +8488,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C241" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D241" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8523,7 +8523,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.305630904096377e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8744,10 +8744,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0002479937307184874</v>
+        <v>0.0002479937307184875</v>
       </c>
       <c r="D249" t="n">
-        <v>5.455862075806725e-05</v>
+        <v>5.45586207580672e-05</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747834e-05</v>
+        <v>8.361934951747836e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408697e-05</v>
+        <v>1.520351809408696e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8840,10 +8840,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C252" t="n">
-        <v>3.51172917544599e-05</v>
+        <v>3.511729175445989e-05</v>
       </c>
       <c r="D252" t="n">
-        <v>2.74830978947947e-05</v>
+        <v>2.748309789479471e-05</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8907,7 +8907,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D254" t="n">
-        <v>6.747092003346557e-05</v>
+        <v>6.747092003346559e-05</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9160,10 +9160,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C262" t="n">
-        <v>8.742022904100009e-05</v>
+        <v>8.74202290410001e-05</v>
       </c>
       <c r="D262" t="n">
-        <v>2.964686028346959e-05</v>
+        <v>2.964686028346958e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9227,7 +9227,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.832206526319647e-05</v>
+        <v>1.832206526319646e-05</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D267" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0008887760284408329</v>
+        <v>0.000888776028440833</v>
       </c>
       <c r="D271" t="n">
-        <v>2.539360081259528e-05</v>
+        <v>2.539360081259517e-05</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860083</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D272" t="n">
-        <v>5.73572092276278e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9544,10 +9544,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C274" t="n">
-        <v>5.96698764087685e-05</v>
+        <v>5.966987640876849e-05</v>
       </c>
       <c r="D274" t="n">
-        <v>1.491746910219211e-05</v>
+        <v>1.491746910219212e-05</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>6.076810889645115e-05</v>
+        <v>6.076810889645114e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.430724355858045e-05</v>
+        <v>2.430724355858046e-05</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196378e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D292" t="n">
-        <v>1.970896947317137e-05</v>
+        <v>1.970896947317136e-05</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>3.420241241015532e-05</v>
+        <v>3.420241241015533e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507766e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10987,7 +10987,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482712e-06</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11208,7 +11208,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>3.78159602260134e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D326" t="n">
         <v>1.260532007533779e-05</v>
@@ -11240,7 +11240,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D327" t="n">
         <v>1.492001380598611e-05</v>
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D398" t="n">
-        <v>3.981525720656151e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>4.862394242925216e-05</v>
+        <v>4.862394242925217e-05</v>
       </c>
       <c r="D422" t="n">
         <v>1.736569372473291e-05</v>
@@ -14240,10 +14240,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C424" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D424" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.305630904096377e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0002479937307184874</v>
+        <v>0.0002479937307184875</v>
       </c>
       <c r="D438" t="n">
-        <v>5.455862075806725e-05</v>
+        <v>5.45586207580672e-05</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747834e-05</v>
+        <v>8.361934951747836e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408697e-05</v>
+        <v>1.520351809408696e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14884,10 +14884,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C447" t="n">
-        <v>3.51172917544599e-05</v>
+        <v>3.511729175445989e-05</v>
       </c>
       <c r="D447" t="n">
-        <v>2.74830978947947e-05</v>
+        <v>2.748309789479471e-05</v>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr"/>
@@ -15027,7 +15027,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D452" t="n">
-        <v>6.747092003346557e-05</v>
+        <v>6.747092003346559e-05</v>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C463" t="n">
-        <v>8.742022904100009e-05</v>
+        <v>8.74202290410001e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>2.964686028346959e-05</v>
+        <v>2.964686028346958e-05</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15416,7 +15416,7 @@
         <v>4.188920305791183e-05</v>
       </c>
       <c r="C466" t="n">
-        <v>1.730206213261575e-05</v>
+        <v>1.730206213261576e-05</v>
       </c>
       <c r="D466" t="n">
         <v>2.458714092529607e-05</v>
@@ -15559,7 +15559,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.832206526319647e-05</v>
+        <v>1.832206526319646e-05</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -17488,10 +17488,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C540" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D540" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0008887760284408329</v>
+        <v>0.000888776028440833</v>
       </c>
       <c r="D547" t="n">
-        <v>2.539360081259528e-05</v>
+        <v>2.539360081259517e-05</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860083</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D548" t="n">
-        <v>5.73572092276278e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17936,10 +17936,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C556" t="n">
-        <v>5.96698764087685e-05</v>
+        <v>5.966987640876849e-05</v>
       </c>
       <c r="D556" t="n">
-        <v>1.491746910219211e-05</v>
+        <v>1.491746910219212e-05</v>
       </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>6.076810889645115e-05</v>
+        <v>6.076810889645114e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.430724355858045e-05</v>
+        <v>2.430724355858046e-05</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
         <v>1.218034981964682e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>1.974056694908277e-05</v>
+        <v>1.974056694908278e-05</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196378e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18779,7 +18779,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D586" t="n">
-        <v>1.970896947317137e-05</v>
+        <v>1.970896947317136e-05</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>3.420241241015532e-05</v>
+        <v>3.420241241015533e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507766e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21719,7 +21719,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482712e-06</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -22248,7 +22248,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>3.78159602260134e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D710" t="n">
         <v>1.260532007533779e-05</v>
@@ -22276,7 +22276,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D711" t="n">
         <v>1.492001380598611e-05</v>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23340,10 +23340,10 @@
         <v>6.743891993347184e-06</v>
       </c>
       <c r="C749" t="n">
-        <v>3.168902057144532e-06</v>
+        <v>3.168616714789963e-06</v>
       </c>
       <c r="D749" t="n">
-        <v>3.574989936202653e-06</v>
+        <v>3.575275278557222e-06</v>
       </c>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr"/>
@@ -23368,10 +23368,10 @@
         <v>8.941126120184445e-06</v>
       </c>
       <c r="C750" t="n">
-        <v>1.909921497506931e-06</v>
+        <v>1.909657336372347e-06</v>
       </c>
       <c r="D750" t="n">
-        <v>7.031204622677515e-06</v>
+        <v>7.031468783812098e-06</v>
       </c>
       <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D36" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>6.068697657482712e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928249e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>2.206548516810006e-05</v>
+        <v>2.206548516810005e-05</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D70" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D72" t="n">
         <v>1.492001380598611e-05</v>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.7271328667238e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418216e-05</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4136,10 +4136,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C105" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D108" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>6.068697657482712e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928249e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>2.206548516810006e-05</v>
+        <v>2.206548516810005e-05</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D181" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D189" t="n">
         <v>1.492001380598611e-05</v>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.7271328667238e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418216e-05</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8328,10 +8328,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0003835999729223549</v>
+        <v>0.0003835999729223548</v>
       </c>
       <c r="D236" t="n">
-        <v>2.256470428955027e-05</v>
+        <v>2.256470428955033e-05</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8523,7 +8523,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011905e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.305630904096377e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8744,10 +8744,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0002479937307184875</v>
+        <v>0.0002479937307184874</v>
       </c>
       <c r="D249" t="n">
-        <v>5.45586207580672e-05</v>
+        <v>5.455862075806725e-05</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747831e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.5203518094087e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8907,7 +8907,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D254" t="n">
-        <v>6.747092003346559e-05</v>
+        <v>6.747092003346557e-05</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192754e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440958e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9192,7 +9192,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>4.256883574234245e-05</v>
+        <v>4.256883574234244e-05</v>
       </c>
       <c r="D263" t="n">
         <v>2.321936495036861e-05</v>
@@ -9320,10 +9320,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D267" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860081</v>
       </c>
       <c r="D272" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.735720922762802e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9544,10 +9544,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C274" t="n">
-        <v>5.966987640876849e-05</v>
+        <v>5.96698764087685e-05</v>
       </c>
       <c r="D274" t="n">
-        <v>1.491746910219212e-05</v>
+        <v>1.491746910219211e-05</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.664680778255077e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D290" t="n">
-        <v>4.099107305520131e-05</v>
+        <v>4.099107305520128e-05</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196373e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>3.420241241015533e-05</v>
+        <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507766e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10987,7 +10987,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>6.068697657482712e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928249e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>2.206548516810006e-05</v>
+        <v>2.206548516810005e-05</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11176,10 +11176,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D325" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11240,7 +11240,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D327" t="n">
         <v>1.492001380598611e-05</v>
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.7271328667238e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418216e-05</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11432,10 +11432,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C333" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0003835999729223549</v>
+        <v>0.0003835999729223548</v>
       </c>
       <c r="D413" t="n">
-        <v>2.256470428955027e-05</v>
+        <v>2.256470428955033e-05</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011905e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.305630904096377e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0002479937307184875</v>
+        <v>0.0002479937307184874</v>
       </c>
       <c r="D438" t="n">
-        <v>5.45586207580672e-05</v>
+        <v>5.455862075806725e-05</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747831e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.5203518094087e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -15027,7 +15027,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D452" t="n">
-        <v>6.747092003346559e-05</v>
+        <v>6.747092003346557e-05</v>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192754e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440958e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15360,10 +15360,10 @@
         <v>3.051106025934401e-05</v>
       </c>
       <c r="C464" t="n">
-        <v>9.572097336264788e-06</v>
+        <v>9.57209733626479e-06</v>
       </c>
       <c r="D464" t="n">
-        <v>2.093896292307923e-05</v>
+        <v>2.093896292307922e-05</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15528,7 +15528,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>4.256883574234245e-05</v>
+        <v>4.256883574234244e-05</v>
       </c>
       <c r="D470" t="n">
         <v>2.321936495036861e-05</v>
@@ -15640,10 +15640,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C474" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17488,10 +17488,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C540" t="n">
-        <v>0.0001623358448741058</v>
+        <v>0.0001623358448741057</v>
       </c>
       <c r="D540" t="n">
-        <v>4.478230203423607e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860081</v>
       </c>
       <c r="D548" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.735720922762802e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17936,10 +17936,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C556" t="n">
-        <v>5.966987640876849e-05</v>
+        <v>5.96698764087685e-05</v>
       </c>
       <c r="D556" t="n">
-        <v>1.491746910219212e-05</v>
+        <v>1.491746910219211e-05</v>
       </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.664680778255077e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
         <v>1.218034981964682e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>1.974056694908278e-05</v>
+        <v>1.974056694908277e-05</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18723,7 +18723,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D584" t="n">
-        <v>4.099107305520131e-05</v>
+        <v>4.099107305520128e-05</v>
       </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196373e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>3.420241241015533e-05</v>
+        <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507766e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21719,7 +21719,7 @@
         <v>4.854958125986163e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>6.068697657482712e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928249e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>2.206548516810006e-05</v>
+        <v>2.206548516810005e-05</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22052,10 +22052,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D703" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22276,7 +22276,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D711" t="n">
         <v>1.492001380598611e-05</v>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.7271328667238e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418216e-05</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311833e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>2.24970280241926e-05</v>
+        <v>2.249702802419259e-05</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1445,7 +1445,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1455,7 +1455,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1517,7 +1517,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1553,7 +1553,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1589,17 +1589,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0.001690140845070423</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001690140845070422</v>
+        <v>0.001690140845070423</v>
       </c>
       <c r="D33" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1661,7 +1661,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1697,7 +1697,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1733,7 +1733,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1743,7 +1743,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D37" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1805,7 +1805,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1841,7 +1841,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1877,7 +1877,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1913,7 +1913,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1949,7 +1949,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1985,7 +1985,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2021,7 +2021,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2057,7 +2057,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2093,7 +2093,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2129,7 +2129,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2165,7 +2165,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2201,7 +2201,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2237,7 +2237,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2273,7 +2273,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2309,7 +2309,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2345,7 +2345,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2381,7 +2381,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2417,7 +2417,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2453,7 +2453,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2489,7 +2489,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2525,7 +2525,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2561,7 +2561,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2597,7 +2597,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2633,7 +2633,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2669,7 +2669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2705,7 +2705,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2741,7 +2741,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2813,7 +2813,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2849,7 +2849,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2885,17 +2885,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>4.932284919928249e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>2.206548516810005e-05</v>
+        <v>2.206548516810006e-05</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2921,17 +2921,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>0.0001183179011167683</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D70" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291305e-05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2993,7 +2993,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3029,7 +3029,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3065,7 +3065,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3137,7 +3137,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3173,7 +3173,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3209,7 +3209,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3245,7 +3245,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3281,7 +3281,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3317,7 +3317,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3353,17 +3353,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3425,7 +3425,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3461,7 +3461,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3497,7 +3497,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3533,7 +3533,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3569,7 +3569,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3605,7 +3605,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3641,7 +3641,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3677,7 +3677,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3713,7 +3713,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3723,7 +3723,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D92" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3777,7 +3777,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3809,7 +3809,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3841,7 +3841,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3873,7 +3873,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3905,7 +3905,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3937,7 +3937,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3969,7 +3969,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4001,7 +4001,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4033,7 +4033,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4065,7 +4065,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4097,7 +4097,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4129,17 +4129,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0.001690140845070423</v>
       </c>
       <c r="C105" t="n">
-        <v>0.001690140845070422</v>
+        <v>0.001690140845070423</v>
       </c>
       <c r="D105" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4193,7 +4193,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4225,7 +4225,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4257,7 +4257,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4289,7 +4289,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4321,7 +4321,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4353,7 +4353,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4363,7 +4363,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D112" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4417,7 +4417,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4449,7 +4449,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4481,7 +4481,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4513,7 +4513,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -4545,7 +4545,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -4577,7 +4577,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -4609,7 +4609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -4641,7 +4641,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -4673,7 +4673,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -4705,7 +4705,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -4737,7 +4737,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4769,7 +4769,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4801,7 +4801,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -4833,7 +4833,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4865,7 +4865,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -4897,7 +4897,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -4929,7 +4929,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4961,7 +4961,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -4993,7 +4993,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -5025,7 +5025,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5057,7 +5057,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5089,7 +5089,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5121,7 +5121,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5153,7 +5153,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5185,7 +5185,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5217,7 +5217,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5249,7 +5249,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5281,7 +5281,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5313,7 +5313,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5345,7 +5345,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5377,7 +5377,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -5409,7 +5409,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -5441,7 +5441,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5473,7 +5473,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5505,7 +5505,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5537,7 +5537,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5569,7 +5569,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5601,7 +5601,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -5633,7 +5633,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -5665,7 +5665,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -5697,7 +5697,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -5729,7 +5729,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -5761,7 +5761,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -5793,7 +5793,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -5825,7 +5825,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5857,7 +5857,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5889,7 +5889,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5921,7 +5921,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5953,7 +5953,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5985,7 +5985,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6017,7 +6017,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -6049,7 +6049,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -6081,7 +6081,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6113,7 +6113,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6145,7 +6145,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6177,7 +6177,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6209,7 +6209,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6273,7 +6273,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6305,7 +6305,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6337,7 +6337,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -6369,7 +6369,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -6401,7 +6401,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -6433,7 +6433,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6465,7 +6465,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -6497,7 +6497,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -6529,17 +6529,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>4.932284919928249e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>2.206548516810005e-05</v>
+        <v>2.206548516810006e-05</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6561,17 +6561,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>0.0001183179011167683</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D181" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291305e-05</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6593,14 +6593,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>2.630726397147124e-05</v>
       </c>
       <c r="C182" t="n">
-        <v>1.315363198573562e-05</v>
+        <v>1.315363198573561e-05</v>
       </c>
       <c r="D182" t="n">
         <v>1.315363198573562e-05</v>
@@ -6625,7 +6625,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -6657,7 +6657,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -6689,7 +6689,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -6721,7 +6721,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -6753,7 +6753,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -6785,7 +6785,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -6817,7 +6817,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -6849,7 +6849,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -6881,7 +6881,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -6913,7 +6913,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -6945,7 +6945,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6977,7 +6977,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -7009,7 +7009,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -7041,7 +7041,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -7073,7 +7073,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -7105,7 +7105,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -7137,17 +7137,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -7201,7 +7201,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -7233,7 +7233,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -7265,7 +7265,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -7297,7 +7297,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -7329,17 +7329,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C205" t="n">
-        <v>3.385888550559488e-05</v>
+        <v>3.385888550559489e-05</v>
       </c>
       <c r="D205" t="n">
-        <v>1.167547776055002e-06</v>
+        <v>1.167547776054995e-06</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -7393,7 +7393,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -7425,7 +7425,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -7457,7 +7457,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -7489,7 +7489,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -7521,17 +7521,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>3.766524531461867e-05</v>
       </c>
       <c r="C211" t="n">
-        <v>2.715401406402741e-05</v>
+        <v>2.715401406402742e-05</v>
       </c>
       <c r="D211" t="n">
-        <v>1.051123125059126e-05</v>
+        <v>1.051123125059125e-05</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -7585,7 +7585,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -7617,7 +7617,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -7649,7 +7649,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -7681,7 +7681,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -7713,7 +7713,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -7745,7 +7745,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -7777,7 +7777,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -7809,7 +7809,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -7841,7 +7841,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -7873,7 +7873,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -7905,7 +7905,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -7937,7 +7937,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -8001,7 +8001,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -8033,7 +8033,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -8043,7 +8043,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D227" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -8097,7 +8097,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -8129,7 +8129,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -8161,17 +8161,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>0.0001651654958268185</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0001596599792992579</v>
+        <v>0.0001596599792992578</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560655e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8193,7 +8193,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -8225,7 +8225,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -8257,7 +8257,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -8289,7 +8289,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -8321,7 +8321,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -8353,7 +8353,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -8385,7 +8385,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -8417,14 +8417,14 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>4.862394242925217e-05</v>
+        <v>4.862394242925216e-05</v>
       </c>
       <c r="D239" t="n">
         <v>1.736569372473291e-05</v>
@@ -8449,7 +8449,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -8459,7 +8459,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8481,7 +8481,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -8513,7 +8513,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -8545,7 +8545,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -8577,7 +8577,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -8609,7 +8609,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -8641,7 +8641,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -8673,7 +8673,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -8705,7 +8705,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -8737,7 +8737,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -8769,17 +8769,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747831e-05</v>
+        <v>8.361934951747833e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.5203518094087e-05</v>
+        <v>1.520351809408698e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -8833,7 +8833,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -8865,7 +8865,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -8897,7 +8897,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -8929,7 +8929,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -8961,17 +8961,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D256" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -8993,7 +8993,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -9025,7 +9025,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -9057,7 +9057,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -9089,7 +9089,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306982e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9121,7 +9121,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -9131,7 +9131,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D261" t="n">
-        <v>3.57110972234622e-05</v>
+        <v>3.571109722346218e-05</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9153,7 +9153,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -9185,7 +9185,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -9217,7 +9217,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -9249,17 +9249,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C265" t="n">
-        <v>5.028464701973672e-05</v>
+        <v>5.028464701973673e-05</v>
       </c>
       <c r="D265" t="n">
-        <v>1.257116175493418e-05</v>
+        <v>1.257116175493417e-05</v>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
@@ -9281,7 +9281,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -9313,7 +9313,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -9345,7 +9345,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -9377,7 +9377,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -9409,7 +9409,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -9441,7 +9441,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -9473,7 +9473,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -9505,7 +9505,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -9537,7 +9537,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -9569,14 +9569,14 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C275" t="n">
-        <v>5.120454272577672e-05</v>
+        <v>5.120454272577673e-05</v>
       </c>
       <c r="D275" t="n">
         <v>1.589106498386174e-05</v>
@@ -9601,7 +9601,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -9611,7 +9611,7 @@
         <v>0.0001090320034890241</v>
       </c>
       <c r="D276" t="n">
-        <v>2.076800066457603e-05</v>
+        <v>2.076800066457601e-05</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9633,7 +9633,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -9643,7 +9643,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D277" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9665,7 +9665,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -9697,7 +9697,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -9729,7 +9729,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -9761,7 +9761,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -9793,7 +9793,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9825,7 +9825,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.664680778255077e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9857,14 +9857,14 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>2.855857721168332e-05</v>
+        <v>2.855857721168331e-05</v>
       </c>
       <c r="D284" t="n">
         <v>1.784911075730207e-05</v>
@@ -9889,7 +9889,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -9921,7 +9921,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -9953,7 +9953,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -9985,7 +9985,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -10017,7 +10017,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -10049,7 +10049,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -10081,7 +10081,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196373e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10113,7 +10113,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -10123,7 +10123,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D292" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10145,7 +10145,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -10177,7 +10177,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -10187,7 +10187,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10209,17 +10209,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>8.008582220202488e-05</v>
+        <v>8.008582220202486e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>1.48996878515395e-05</v>
+        <v>1.489968785153952e-05</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10241,7 +10241,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -10273,7 +10273,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -10305,7 +10305,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -10337,7 +10337,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -10369,7 +10369,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -10401,7 +10401,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -10433,7 +10433,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -10465,7 +10465,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -10497,7 +10497,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -10529,7 +10529,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -10561,7 +10561,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -10593,7 +10593,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -10625,7 +10625,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -10657,7 +10657,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -10689,7 +10689,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -10721,7 +10721,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -10753,7 +10753,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -10785,7 +10785,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -10817,7 +10817,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -10849,7 +10849,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -10881,7 +10881,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -10913,7 +10913,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -10945,7 +10945,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -10977,7 +10977,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -11009,7 +11009,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11041,7 +11041,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -11073,7 +11073,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -11105,7 +11105,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -11137,17 +11137,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>4.932284919928249e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>2.206548516810005e-05</v>
+        <v>2.206548516810006e-05</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11169,17 +11169,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>0.0001183179011167683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D325" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291305e-05</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11201,7 +11201,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -11233,7 +11233,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -11265,7 +11265,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -11297,7 +11297,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11329,7 +11329,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -11361,7 +11361,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -11393,7 +11393,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -11425,17 +11425,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>0.001690140845070423</v>
       </c>
       <c r="C333" t="n">
-        <v>0.001690140845070422</v>
+        <v>0.001690140845070423</v>
       </c>
       <c r="D333" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -11489,7 +11489,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -11521,7 +11521,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -11553,7 +11553,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -11585,7 +11585,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -11617,7 +11617,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -11649,7 +11649,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -11681,7 +11681,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -11713,7 +11713,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -11745,7 +11745,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -11777,7 +11777,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -11809,7 +11809,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -11841,7 +11841,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -11873,7 +11873,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -11905,7 +11905,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -11937,7 +11937,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -11969,7 +11969,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -12001,7 +12001,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -12033,7 +12033,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -12065,7 +12065,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -12097,7 +12097,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -12129,7 +12129,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -12161,7 +12161,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -12193,7 +12193,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -12225,7 +12225,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -12257,7 +12257,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -12289,7 +12289,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -12321,7 +12321,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -12353,7 +12353,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -12385,7 +12385,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -12417,7 +12417,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -12449,7 +12449,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -12481,7 +12481,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -12513,7 +12513,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -12545,7 +12545,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -12577,7 +12577,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -12609,7 +12609,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -12641,7 +12641,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -12673,7 +12673,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -12705,7 +12705,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -12737,7 +12737,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -12769,7 +12769,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -12801,7 +12801,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -12833,7 +12833,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -12865,7 +12865,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -12897,7 +12897,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -12929,7 +12929,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -12961,7 +12961,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -12993,7 +12993,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -13025,7 +13025,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -13057,7 +13057,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -13089,7 +13089,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -13121,7 +13121,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -13153,7 +13153,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -13185,17 +13185,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B388" t="n">
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -13249,7 +13249,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -13281,7 +13281,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -13313,7 +13313,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -13345,7 +13345,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -13377,7 +13377,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -13409,7 +13409,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -13441,7 +13441,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -13473,7 +13473,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -13505,7 +13505,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -13515,7 +13515,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D398" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13533,7 +13533,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -13561,7 +13561,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -13589,7 +13589,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -13617,7 +13617,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -13645,7 +13645,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -13673,7 +13673,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -13701,17 +13701,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B405" t="n">
         <v>0.0001651654958268185</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0001596599792992579</v>
+        <v>0.0001596599792992578</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560655e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -13757,7 +13757,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -13785,7 +13785,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -13813,7 +13813,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -13841,7 +13841,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -13869,7 +13869,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -13897,7 +13897,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -13925,7 +13925,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -13953,7 +13953,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -13981,7 +13981,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -14009,7 +14009,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -14037,7 +14037,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -14065,7 +14065,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -14093,7 +14093,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -14121,7 +14121,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -14149,7 +14149,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -14177,14 +14177,14 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B422" t="n">
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>4.862394242925217e-05</v>
+        <v>4.862394242925216e-05</v>
       </c>
       <c r="D422" t="n">
         <v>1.736569372473291e-05</v>
@@ -14205,7 +14205,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -14215,7 +14215,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D423" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
@@ -14233,7 +14233,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -14261,7 +14261,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -14289,7 +14289,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -14317,7 +14317,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -14345,7 +14345,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -14373,7 +14373,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -14401,7 +14401,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -14429,7 +14429,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -14457,7 +14457,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -14485,7 +14485,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -14513,7 +14513,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -14541,7 +14541,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -14569,7 +14569,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -14597,7 +14597,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -14625,7 +14625,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -14653,17 +14653,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B439" t="n">
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747831e-05</v>
+        <v>8.361934951747833e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.5203518094087e-05</v>
+        <v>1.520351809408698e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14681,7 +14681,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -14709,7 +14709,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -14737,7 +14737,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -14765,7 +14765,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -14793,7 +14793,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -14821,7 +14821,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -14849,7 +14849,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -14877,7 +14877,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -14905,7 +14905,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -14933,7 +14933,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -14961,7 +14961,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -14989,7 +14989,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -15017,7 +15017,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -15045,7 +15045,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -15073,17 +15073,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B454" t="n">
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D454" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15101,7 +15101,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -15129,7 +15129,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -15157,7 +15157,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -15185,7 +15185,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -15213,7 +15213,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -15241,7 +15241,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -15269,7 +15269,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306982e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15297,7 +15297,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -15307,7 +15307,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D462" t="n">
-        <v>3.57110972234622e-05</v>
+        <v>3.571109722346218e-05</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15325,7 +15325,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -15353,7 +15353,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -15381,7 +15381,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -15409,7 +15409,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -15437,7 +15437,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -15465,7 +15465,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -15493,7 +15493,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -15521,7 +15521,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -15549,7 +15549,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -15577,17 +15577,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B472" t="n">
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C472" t="n">
-        <v>5.028464701973672e-05</v>
+        <v>5.028464701973673e-05</v>
       </c>
       <c r="D472" t="n">
-        <v>1.257116175493418e-05</v>
+        <v>1.257116175493417e-05</v>
       </c>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
@@ -15605,7 +15605,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -15633,17 +15633,17 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B474" t="n">
         <v>0.001690140845070423</v>
       </c>
       <c r="C474" t="n">
-        <v>0.001690140845070422</v>
+        <v>0.001690140845070423</v>
       </c>
       <c r="D474" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -15661,7 +15661,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -15689,7 +15689,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -15717,7 +15717,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -15745,7 +15745,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -15773,7 +15773,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -15801,7 +15801,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -15829,7 +15829,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -15857,7 +15857,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -15885,7 +15885,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -15913,7 +15913,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -15941,7 +15941,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -15969,7 +15969,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -15997,7 +15997,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -16025,7 +16025,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -16053,7 +16053,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -16081,7 +16081,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -16109,7 +16109,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -16137,7 +16137,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -16165,7 +16165,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -16193,7 +16193,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -16221,7 +16221,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -16249,7 +16249,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -16277,7 +16277,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -16305,7 +16305,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -16333,7 +16333,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -16361,7 +16361,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -16389,7 +16389,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -16417,7 +16417,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -16445,7 +16445,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -16473,7 +16473,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -16501,7 +16501,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -16529,7 +16529,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -16557,7 +16557,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -16585,7 +16585,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -16613,7 +16613,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -16641,7 +16641,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -16669,7 +16669,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -16697,7 +16697,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -16725,7 +16725,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -16753,7 +16753,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -16781,7 +16781,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -16809,7 +16809,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -16837,7 +16837,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -16865,7 +16865,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -16893,7 +16893,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -16921,7 +16921,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -16949,7 +16949,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -16977,7 +16977,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -17005,7 +17005,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -17033,7 +17033,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -17061,7 +17061,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -17089,7 +17089,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -17117,7 +17117,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -17145,7 +17145,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -17173,7 +17173,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -17201,7 +17201,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -17229,7 +17229,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -17257,7 +17257,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -17285,7 +17285,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -17313,7 +17313,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -17341,7 +17341,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -17369,7 +17369,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -17397,7 +17397,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -17425,7 +17425,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -17453,7 +17453,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -17481,7 +17481,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -17509,7 +17509,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -17537,7 +17537,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -17565,7 +17565,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -17593,7 +17593,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -17621,7 +17621,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -17649,7 +17649,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -17677,7 +17677,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -17705,7 +17705,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -17733,7 +17733,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -17761,7 +17761,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -17771,7 +17771,7 @@
         <v>1.556635591608004e-05</v>
       </c>
       <c r="D550" t="n">
-        <v>2.594392652680007e-05</v>
+        <v>2.594392652680008e-05</v>
       </c>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr"/>
@@ -17789,7 +17789,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -17817,7 +17817,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -17845,7 +17845,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -17873,7 +17873,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -17901,7 +17901,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -17929,7 +17929,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -17957,14 +17957,14 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B557" t="n">
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C557" t="n">
-        <v>5.120454272577672e-05</v>
+        <v>5.120454272577673e-05</v>
       </c>
       <c r="D557" t="n">
         <v>1.589106498386174e-05</v>
@@ -17985,7 +17985,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -17995,7 +17995,7 @@
         <v>0.0001090320034890241</v>
       </c>
       <c r="D558" t="n">
-        <v>2.076800066457603e-05</v>
+        <v>2.076800066457601e-05</v>
       </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
@@ -18013,7 +18013,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -18023,7 +18023,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D559" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18041,7 +18041,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -18069,7 +18069,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -18097,7 +18097,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -18125,7 +18125,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -18153,7 +18153,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -18181,7 +18181,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -18209,7 +18209,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -18237,7 +18237,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18265,7 +18265,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.664680778255077e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18293,7 +18293,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -18321,7 +18321,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -18349,7 +18349,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -18377,7 +18377,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -18405,7 +18405,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -18433,7 +18433,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -18461,14 +18461,14 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B575" t="n">
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>2.855857721168332e-05</v>
+        <v>2.855857721168331e-05</v>
       </c>
       <c r="D575" t="n">
         <v>1.784911075730207e-05</v>
@@ -18489,7 +18489,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -18517,7 +18517,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -18545,7 +18545,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -18573,7 +18573,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -18601,7 +18601,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -18629,7 +18629,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -18657,7 +18657,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -18685,7 +18685,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -18713,7 +18713,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -18741,7 +18741,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196373e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18769,7 +18769,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -18779,7 +18779,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D586" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18797,7 +18797,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -18825,7 +18825,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -18853,7 +18853,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -18881,7 +18881,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -18909,7 +18909,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -18937,7 +18937,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -18965,7 +18965,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -18993,7 +18993,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -19003,7 +19003,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19021,17 +19021,17 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B595" t="n">
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>8.008582220202488e-05</v>
+        <v>8.008582220202486e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>1.48996878515395e-05</v>
+        <v>1.489968785153952e-05</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -19049,7 +19049,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -19077,7 +19077,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -19105,7 +19105,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -19133,7 +19133,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -19161,7 +19161,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -19189,7 +19189,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -19217,7 +19217,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -19245,7 +19245,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -19273,7 +19273,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -19301,7 +19301,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -19329,7 +19329,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -19357,7 +19357,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -19385,7 +19385,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -19413,7 +19413,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -19441,7 +19441,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -19469,7 +19469,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -19497,7 +19497,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -19525,7 +19525,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -19553,7 +19553,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -19581,7 +19581,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -19609,7 +19609,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -19637,7 +19637,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -19665,7 +19665,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -19693,7 +19693,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -19721,7 +19721,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -19749,7 +19749,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -19777,7 +19777,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -19805,7 +19805,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -19833,7 +19833,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -19861,7 +19861,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -19889,7 +19889,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -19917,7 +19917,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -19945,7 +19945,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -19973,7 +19973,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -20001,7 +20001,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -20029,7 +20029,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -20057,7 +20057,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -20085,7 +20085,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -20113,7 +20113,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -20141,7 +20141,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -20169,7 +20169,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -20197,7 +20197,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -20225,7 +20225,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -20253,7 +20253,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -20281,7 +20281,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -20309,7 +20309,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -20337,7 +20337,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -20365,7 +20365,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -20393,7 +20393,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -20421,7 +20421,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -20449,7 +20449,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -20477,7 +20477,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -20505,7 +20505,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -20533,7 +20533,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -20561,7 +20561,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -20589,7 +20589,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -20617,7 +20617,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -20645,7 +20645,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -20673,7 +20673,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -20701,7 +20701,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -20729,7 +20729,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -20757,7 +20757,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -20785,7 +20785,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -20813,7 +20813,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -20841,7 +20841,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -20869,7 +20869,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -20897,7 +20897,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -20925,7 +20925,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -20953,7 +20953,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -20981,7 +20981,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -21009,7 +21009,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -21037,7 +21037,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -21065,7 +21065,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -21093,7 +21093,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -21121,7 +21121,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -21149,7 +21149,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -21177,7 +21177,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -21205,7 +21205,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -21233,7 +21233,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -21261,7 +21261,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -21289,7 +21289,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -21317,7 +21317,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -21345,7 +21345,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -21373,7 +21373,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -21401,7 +21401,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -21429,7 +21429,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -21457,7 +21457,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -21485,7 +21485,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -21513,7 +21513,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -21541,7 +21541,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -21569,7 +21569,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -21597,7 +21597,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -21625,7 +21625,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -21653,7 +21653,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -21681,7 +21681,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -21709,7 +21709,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -21737,7 +21737,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21765,7 +21765,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -21793,7 +21793,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -21821,7 +21821,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -21849,7 +21849,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -21877,7 +21877,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -21905,7 +21905,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -21933,7 +21933,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -21961,7 +21961,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -21989,7 +21989,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -22017,17 +22017,17 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B702" t="n">
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>4.932284919928249e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>2.206548516810005e-05</v>
+        <v>2.206548516810006e-05</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22045,17 +22045,17 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B703" t="n">
         <v>0.0001183179011167683</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D703" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291305e-05</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22073,14 +22073,14 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B704" t="n">
         <v>2.630726397147124e-05</v>
       </c>
       <c r="C704" t="n">
-        <v>1.315363198573562e-05</v>
+        <v>1.315363198573561e-05</v>
       </c>
       <c r="D704" t="n">
         <v>1.315363198573562e-05</v>
@@ -22101,7 +22101,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -22129,7 +22129,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -22157,7 +22157,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -22185,7 +22185,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -22213,7 +22213,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -22241,7 +22241,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -22269,7 +22269,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -22297,7 +22297,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -22325,7 +22325,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -22353,7 +22353,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -22381,7 +22381,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -22409,7 +22409,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -22437,7 +22437,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -22465,7 +22465,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -22493,7 +22493,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -22521,7 +22521,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -22549,17 +22549,17 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B721" t="n">
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311833e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>2.249702802419259e-05</v>
+        <v>2.24970280241926e-05</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22577,7 +22577,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -22605,7 +22605,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -22633,7 +22633,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -22661,7 +22661,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -22689,7 +22689,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -22717,17 +22717,17 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B727" t="n">
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C727" t="n">
-        <v>3.385888550559488e-05</v>
+        <v>3.385888550559489e-05</v>
       </c>
       <c r="D727" t="n">
-        <v>1.167547776055002e-06</v>
+        <v>1.167547776054995e-06</v>
       </c>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr"/>
@@ -22745,7 +22745,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -22773,7 +22773,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -22801,7 +22801,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -22829,7 +22829,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -22857,7 +22857,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -22885,17 +22885,17 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B733" t="n">
         <v>3.766524531461867e-05</v>
       </c>
       <c r="C733" t="n">
-        <v>2.715401406402741e-05</v>
+        <v>2.715401406402742e-05</v>
       </c>
       <c r="D733" t="n">
-        <v>1.051123125059126e-05</v>
+        <v>1.051123125059125e-05</v>
       </c>
       <c r="E733" t="inlineStr"/>
       <c r="F733" t="inlineStr"/>
@@ -22913,7 +22913,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -22941,7 +22941,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -22969,7 +22969,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -22997,7 +22997,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -23025,7 +23025,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -23053,7 +23053,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -23081,7 +23081,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -23109,7 +23109,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -23137,7 +23137,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -23165,7 +23165,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -23193,7 +23193,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -23221,7 +23221,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -23249,7 +23249,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23277,7 +23277,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -23305,7 +23305,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B748" t="n">

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -23333,7 +23333,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -23361,7 +23361,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B750" t="n">

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D37" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C68" t="n">
-        <v>8.224518385910852e-05</v>
+        <v>8.22451838591085e-05</v>
       </c>
       <c r="D68" t="n">
-        <v>2.467355515773255e-05</v>
+        <v>2.467355515773257e-05</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D92" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D112" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C179" t="n">
-        <v>8.224518385910852e-05</v>
+        <v>8.22451838591085e-05</v>
       </c>
       <c r="D179" t="n">
-        <v>2.467355515773255e-05</v>
+        <v>2.467355515773257e-05</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>2.630726397147124e-05</v>
       </c>
       <c r="C182" t="n">
-        <v>1.315363198573561e-05</v>
+        <v>1.315363198573562e-05</v>
       </c>
       <c r="D182" t="n">
         <v>1.315363198573562e-05</v>
@@ -6827,7 +6827,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D227" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8136,10 +8136,10 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="C230" t="n">
-        <v>0.000112632465573642</v>
+        <v>0.0001126324655736421</v>
       </c>
       <c r="D230" t="n">
-        <v>3.427944604415193e-05</v>
+        <v>3.427944604415192e-05</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8168,10 +8168,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0001596599792992578</v>
+        <v>0.0001596599792992579</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560655e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D240" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8523,7 +8523,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001331164744948835</v>
       </c>
       <c r="D244" t="n">
-        <v>2.42029953627061e-05</v>
+        <v>2.420299536270607e-05</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8872,10 +8872,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C253" t="n">
-        <v>8.979401253524414e-05</v>
+        <v>8.979401253524417e-05</v>
       </c>
       <c r="D253" t="n">
-        <v>3.142790438733547e-05</v>
+        <v>3.142790438733544e-05</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306982e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D261" t="n">
-        <v>3.571109722346218e-05</v>
+        <v>3.57110972234622e-05</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D271" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9512,10 +9512,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0001318629153132404</v>
+        <v>0.0001318629153132403</v>
       </c>
       <c r="D273" t="n">
-        <v>4.615202035963413e-05</v>
+        <v>4.615202035963416e-05</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9576,7 +9576,7 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C275" t="n">
-        <v>5.120454272577673e-05</v>
+        <v>5.120454272577672e-05</v>
       </c>
       <c r="D275" t="n">
         <v>1.589106498386174e-05</v>
@@ -9643,7 +9643,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D277" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196373e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10187,7 +10187,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11112,10 +11112,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C323" t="n">
-        <v>8.224518385910852e-05</v>
+        <v>8.22451838591085e-05</v>
       </c>
       <c r="D323" t="n">
-        <v>2.467355515773255e-05</v>
+        <v>2.467355515773257e-05</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11243,7 +11243,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D398" t="n">
-        <v>3.981525720656172e-05</v>
+        <v>3.981525720656194e-05</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13680,10 +13680,10 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="C404" t="n">
-        <v>0.000112632465573642</v>
+        <v>0.0001126324655736421</v>
       </c>
       <c r="D404" t="n">
-        <v>3.427944604415193e-05</v>
+        <v>3.427944604415192e-05</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13708,10 +13708,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0001596599792992578</v>
+        <v>0.0001596599792992579</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560655e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14215,7 +14215,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D423" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001331164744948835</v>
       </c>
       <c r="D430" t="n">
-        <v>2.42029953627061e-05</v>
+        <v>2.420299536270607e-05</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C448" t="n">
-        <v>8.979401253524414e-05</v>
+        <v>8.979401253524417e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>3.142790438733547e-05</v>
+        <v>3.142790438733544e-05</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306982e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15307,7 +15307,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D462" t="n">
-        <v>3.571109722346218e-05</v>
+        <v>3.57110972234622e-05</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15360,10 +15360,10 @@
         <v>3.051106025934401e-05</v>
       </c>
       <c r="C464" t="n">
-        <v>9.57209733626479e-06</v>
+        <v>9.572097336264788e-06</v>
       </c>
       <c r="D464" t="n">
-        <v>2.093896292307922e-05</v>
+        <v>2.093896292307923e-05</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D547" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17740,10 +17740,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C549" t="n">
-        <v>0.0001318629153132404</v>
+        <v>0.0001318629153132403</v>
       </c>
       <c r="D549" t="n">
-        <v>4.615202035963413e-05</v>
+        <v>4.615202035963416e-05</v>
       </c>
       <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr"/>
@@ -17771,7 +17771,7 @@
         <v>1.556635591608004e-05</v>
       </c>
       <c r="D550" t="n">
-        <v>2.594392652680008e-05</v>
+        <v>2.594392652680007e-05</v>
       </c>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr"/>
@@ -17964,7 +17964,7 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C557" t="n">
-        <v>5.120454272577673e-05</v>
+        <v>5.120454272577672e-05</v>
       </c>
       <c r="D557" t="n">
         <v>1.589106498386174e-05</v>
@@ -18023,7 +18023,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D559" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196373e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19003,7 +19003,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21996,10 +21996,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C701" t="n">
-        <v>8.224518385910852e-05</v>
+        <v>8.22451838591085e-05</v>
       </c>
       <c r="D701" t="n">
-        <v>2.467355515773255e-05</v>
+        <v>2.467355515773257e-05</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22080,7 +22080,7 @@
         <v>2.630726397147124e-05</v>
       </c>
       <c r="C704" t="n">
-        <v>1.315363198573561e-05</v>
+        <v>1.315363198573562e-05</v>
       </c>
       <c r="D704" t="n">
         <v>1.315363198573562e-05</v>
@@ -22279,7 +22279,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D36" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D37" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C66" t="n">
-        <v>8.448800270361609e-05</v>
+        <v>8.448800270361608e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>1.689760054072321e-05</v>
+        <v>1.689760054072323e-05</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>4.932284919928247e-05</v>
+        <v>4.932284919928248e-05</v>
       </c>
       <c r="D69" t="n">
         <v>2.206548516810006e-05</v>
@@ -2928,10 +2928,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D70" t="n">
-        <v>1.145011946291305e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.781596022601338e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>1.260532007533779e-05</v>
+        <v>1.26053200753378e-05</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311831e-05</v>
       </c>
       <c r="D82" t="n">
         <v>2.24970280241926e-05</v>
@@ -3723,7 +3723,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D92" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D108" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D112" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>1.927855368006169e-05</v>
+        <v>1.92785536800617e-05</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C171" t="n">
-        <v>8.448800270361609e-05</v>
+        <v>8.448800270361608e-05</v>
       </c>
       <c r="D171" t="n">
-        <v>1.689760054072321e-05</v>
+        <v>1.689760054072323e-05</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D175" t="n">
-        <v>1.838566150642434e-05</v>
+        <v>1.838566150642433e-05</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>4.932284919928247e-05</v>
+        <v>4.932284919928248e-05</v>
       </c>
       <c r="D180" t="n">
         <v>2.206548516810006e-05</v>
@@ -6568,10 +6568,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D181" t="n">
-        <v>1.145011946291305e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.781596022601338e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>1.260532007533779e-05</v>
+        <v>1.26053200753378e-05</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311831e-05</v>
       </c>
       <c r="D199" t="n">
         <v>2.24970280241926e-05</v>
@@ -7336,10 +7336,10 @@
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C205" t="n">
-        <v>3.385888550559489e-05</v>
+        <v>3.385888550559488e-05</v>
       </c>
       <c r="D205" t="n">
-        <v>1.167547776054995e-06</v>
+        <v>1.167547776055002e-06</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D227" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8136,10 +8136,10 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0001126324655736421</v>
+        <v>0.000112632465573642</v>
       </c>
       <c r="D230" t="n">
-        <v>3.427944604415192e-05</v>
+        <v>3.427944604415193e-05</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001596599792992579</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560601e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8328,10 +8328,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0003835999729223548</v>
+        <v>0.0003835999729223549</v>
       </c>
       <c r="D236" t="n">
-        <v>2.256470428955033e-05</v>
+        <v>2.256470428955027e-05</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8424,7 +8424,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>4.862394242925216e-05</v>
+        <v>4.862394242925217e-05</v>
       </c>
       <c r="D239" t="n">
         <v>1.736569372473291e-05</v>
@@ -8523,7 +8523,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011905e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.30563090409638e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8715,7 +8715,7 @@
         <v>0.0001756697408871322</v>
       </c>
       <c r="D248" t="n">
-        <v>3.29380764163373e-05</v>
+        <v>3.293807641633728e-05</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>6.127332417458382e-05</v>
+        <v>6.127332417458383e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>1.934947079197384e-05</v>
+        <v>1.934947079197383e-05</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8872,10 +8872,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C253" t="n">
-        <v>8.979401253524417e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D253" t="n">
-        <v>3.142790438733544e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192754e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440958e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0002526792715866515</v>
+        <v>0.0002526792715866516</v>
       </c>
       <c r="D256" t="n">
-        <v>6.002342849951113e-05</v>
+        <v>6.002342849951108e-05</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306984e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9160,10 +9160,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C262" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100011e-05</v>
       </c>
       <c r="D262" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346956e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9192,7 +9192,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>4.256883574234244e-05</v>
+        <v>4.256883574234245e-05</v>
       </c>
       <c r="D263" t="n">
         <v>2.321936495036861e-05</v>
@@ -9227,7 +9227,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.832206526319646e-05</v>
+        <v>1.832206526319647e-05</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D267" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860081</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D272" t="n">
-        <v>5.735720922762802e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9611,7 +9611,7 @@
         <v>0.0001090320034890241</v>
       </c>
       <c r="D276" t="n">
-        <v>2.076800066457601e-05</v>
+        <v>2.076800066457603e-05</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D277" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D290" t="n">
-        <v>4.099107305520128e-05</v>
+        <v>4.099107305520131e-05</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196373e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10187,7 +10187,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>8.008582220202486e-05</v>
+        <v>8.008582220202488e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>1.489968785153952e-05</v>
+        <v>1.48996878515395e-05</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11048,10 +11048,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C321" t="n">
-        <v>8.448800270361609e-05</v>
+        <v>8.448800270361608e-05</v>
       </c>
       <c r="D321" t="n">
-        <v>1.689760054072321e-05</v>
+        <v>1.689760054072323e-05</v>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
@@ -11144,7 +11144,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>4.932284919928247e-05</v>
+        <v>4.932284919928248e-05</v>
       </c>
       <c r="D324" t="n">
         <v>2.206548516810006e-05</v>
@@ -11176,10 +11176,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D325" t="n">
-        <v>1.145011946291305e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.781596022601338e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>1.260532007533779e-05</v>
+        <v>1.26053200753378e-05</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11243,7 +11243,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13192,7 +13192,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311831e-05</v>
       </c>
       <c r="D388" t="n">
         <v>2.24970280241926e-05</v>
@@ -13515,7 +13515,7 @@
         <v>0.001181185963794659</v>
       </c>
       <c r="D398" t="n">
-        <v>3.981525720656194e-05</v>
+        <v>3.981525720656172e-05</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349952e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13680,10 +13680,10 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="C404" t="n">
-        <v>0.0001126324655736421</v>
+        <v>0.000112632465573642</v>
       </c>
       <c r="D404" t="n">
-        <v>3.427944604415192e-05</v>
+        <v>3.427944604415193e-05</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001596599792992579</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560601e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0003835999729223548</v>
+        <v>0.0003835999729223549</v>
       </c>
       <c r="D413" t="n">
-        <v>2.256470428955033e-05</v>
+        <v>2.256470428955027e-05</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>4.862394242925216e-05</v>
+        <v>4.862394242925217e-05</v>
       </c>
       <c r="D422" t="n">
         <v>1.736569372473291e-05</v>
@@ -14355,7 +14355,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011905e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.30563090409638e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14607,7 +14607,7 @@
         <v>0.0001756697408871322</v>
       </c>
       <c r="D437" t="n">
-        <v>3.29380764163373e-05</v>
+        <v>3.293807641633728e-05</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
         <v>2.731046537032991e-05</v>
       </c>
       <c r="C441" t="n">
-        <v>1.365523268516496e-05</v>
+        <v>1.365523268516495e-05</v>
       </c>
       <c r="D441" t="n">
         <v>1.365523268516495e-05</v>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>6.127332417458382e-05</v>
+        <v>6.127332417458383e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>1.934947079197384e-05</v>
+        <v>1.934947079197383e-05</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C448" t="n">
-        <v>8.979401253524417e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>3.142790438733544e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192754e-05</v>
+        <v>8.611261808192752e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440958e-05</v>
+        <v>3.616729959440959e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0002526792715866515</v>
+        <v>0.0002526792715866516</v>
       </c>
       <c r="D454" t="n">
-        <v>6.002342849951113e-05</v>
+        <v>6.002342849951108e-05</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306984e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C463" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100011e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346956e-05</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15360,10 +15360,10 @@
         <v>3.051106025934401e-05</v>
       </c>
       <c r="C464" t="n">
-        <v>9.572097336264788e-06</v>
+        <v>9.57209733626479e-06</v>
       </c>
       <c r="D464" t="n">
-        <v>2.093896292307923e-05</v>
+        <v>2.093896292307922e-05</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15416,7 +15416,7 @@
         <v>4.188920305791183e-05</v>
       </c>
       <c r="C466" t="n">
-        <v>1.730206213261576e-05</v>
+        <v>1.730206213261575e-05</v>
       </c>
       <c r="D466" t="n">
         <v>2.458714092529607e-05</v>
@@ -15528,7 +15528,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>4.256883574234244e-05</v>
+        <v>4.256883574234245e-05</v>
       </c>
       <c r="D470" t="n">
         <v>2.321936495036861e-05</v>
@@ -15559,7 +15559,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.832206526319646e-05</v>
+        <v>1.832206526319647e-05</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D540" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.47823020342361e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860081</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D548" t="n">
-        <v>5.735720922762802e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17995,7 +17995,7 @@
         <v>0.0001090320034890241</v>
       </c>
       <c r="D558" t="n">
-        <v>2.076800066457601e-05</v>
+        <v>2.076800066457603e-05</v>
       </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D559" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
         <v>1.218034981964682e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>1.974056694908277e-05</v>
+        <v>1.974056694908278e-05</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18723,7 +18723,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D584" t="n">
-        <v>4.099107305520128e-05</v>
+        <v>4.099107305520131e-05</v>
       </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196373e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -19003,7 +19003,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507767e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>8.008582220202486e-05</v>
+        <v>8.008582220202488e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>1.489968785153952e-05</v>
+        <v>1.48996878515395e-05</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241927</v>
+        <v>0.0007840209072241925</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429718e-05</v>
+        <v>4.666791114429729e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>1.927855368006169e-05</v>
+        <v>1.92785536800617e-05</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21772,10 +21772,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C693" t="n">
-        <v>8.448800270361609e-05</v>
+        <v>8.448800270361608e-05</v>
       </c>
       <c r="D693" t="n">
-        <v>1.689760054072321e-05</v>
+        <v>1.689760054072323e-05</v>
       </c>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="inlineStr"/>
@@ -21887,7 +21887,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D697" t="n">
-        <v>1.838566150642434e-05</v>
+        <v>1.838566150642433e-05</v>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr"/>
@@ -22024,7 +22024,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>4.932284919928247e-05</v>
+        <v>4.932284919928248e-05</v>
       </c>
       <c r="D702" t="n">
         <v>2.206548516810006e-05</v>
@@ -22052,10 +22052,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D703" t="n">
-        <v>1.145011946291305e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22248,10 +22248,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.781596022601338e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>1.260532007533779e-05</v>
+        <v>1.26053200753378e-05</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22279,7 +22279,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392302e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425969e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22556,7 +22556,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311832e-05</v>
+        <v>3.226547440311831e-05</v>
       </c>
       <c r="D721" t="n">
         <v>2.24970280241926e-05</v>
@@ -22724,10 +22724,10 @@
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C727" t="n">
-        <v>3.385888550559489e-05</v>
+        <v>3.385888550559488e-05</v>
       </c>
       <c r="D727" t="n">
-        <v>1.167547776054995e-06</v>
+        <v>1.167547776055002e-06</v>
       </c>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D36" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C66" t="n">
-        <v>8.448800270361608e-05</v>
+        <v>8.448800270361609e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>1.689760054072323e-05</v>
+        <v>1.689760054072321e-05</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C68" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D68" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D69" t="n">
         <v>2.206548516810006e-05</v>
@@ -2928,10 +2928,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D70" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291307e-05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>3.781596022601338e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>1.26053200753378e-05</v>
+        <v>1.260532007533779e-05</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>6.7271328667238e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>1.462420188418216e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>3.530754034834828e-05</v>
+        <v>3.530754034834829e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>2.159304120477498e-05</v>
+        <v>2.159304120477497e-05</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>3.226547440311831e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D82" t="n">
         <v>2.24970280241926e-05</v>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D108" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>1.92785536800617e-05</v>
+        <v>1.927855368006169e-05</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C171" t="n">
-        <v>8.448800270361608e-05</v>
+        <v>8.448800270361609e-05</v>
       </c>
       <c r="D171" t="n">
-        <v>1.689760054072323e-05</v>
+        <v>1.689760054072321e-05</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C179" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D179" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D180" t="n">
         <v>2.206548516810006e-05</v>
@@ -6568,10 +6568,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D181" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291307e-05</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>3.781596022601338e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>1.26053200753378e-05</v>
+        <v>1.260532007533779e-05</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>6.7271328667238e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>1.462420188418216e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>3.530754034834828e-05</v>
+        <v>3.530754034834829e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>2.159304120477498e-05</v>
+        <v>2.159304120477497e-05</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>3.226547440311831e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D199" t="n">
         <v>2.24970280241926e-05</v>
@@ -7528,10 +7528,10 @@
         <v>3.766524531461867e-05</v>
       </c>
       <c r="C211" t="n">
-        <v>2.715401406402742e-05</v>
+        <v>2.715401406402741e-05</v>
       </c>
       <c r="D211" t="n">
-        <v>1.051123125059125e-05</v>
+        <v>1.051123125059126e-05</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001596599792992579</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560601e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8424,7 +8424,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>4.862394242925217e-05</v>
+        <v>4.862394242925216e-05</v>
       </c>
       <c r="D239" t="n">
         <v>1.736569372473291e-05</v>
@@ -8523,7 +8523,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.30563090409638e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001331164744948835</v>
       </c>
       <c r="D244" t="n">
-        <v>2.420299536270607e-05</v>
+        <v>2.42029953627061e-05</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8715,7 +8715,7 @@
         <v>0.0001756697408871322</v>
       </c>
       <c r="D248" t="n">
-        <v>3.293807641633728e-05</v>
+        <v>3.29380764163373e-05</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747833e-05</v>
+        <v>8.361934951747836e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408698e-05</v>
+        <v>1.520351809408696e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8840,10 +8840,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C252" t="n">
-        <v>3.511729175445989e-05</v>
+        <v>3.51172917544599e-05</v>
       </c>
       <c r="D252" t="n">
-        <v>2.748309789479471e-05</v>
+        <v>2.74830978947947e-05</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8872,10 +8872,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C253" t="n">
-        <v>8.979401253524414e-05</v>
+        <v>8.979401253524415e-05</v>
       </c>
       <c r="D253" t="n">
-        <v>3.142790438733547e-05</v>
+        <v>3.142790438733546e-05</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D256" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9160,10 +9160,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C262" t="n">
-        <v>8.742022904100011e-05</v>
+        <v>8.74202290410001e-05</v>
       </c>
       <c r="D262" t="n">
-        <v>2.964686028346956e-05</v>
+        <v>2.964686028346958e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9227,7 +9227,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.832206526319647e-05</v>
+        <v>1.832206526319646e-05</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D267" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0008887760284408329</v>
+        <v>0.000888776028440833</v>
       </c>
       <c r="D271" t="n">
-        <v>2.539360081259528e-05</v>
+        <v>2.539360081259517e-05</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860081</v>
       </c>
       <c r="D272" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.735720922762802e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9512,10 +9512,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0001318629153132403</v>
+        <v>0.0001318629153132404</v>
       </c>
       <c r="D273" t="n">
-        <v>4.615202035963416e-05</v>
+        <v>4.615202035963413e-05</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9864,7 +9864,7 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>2.855857721168331e-05</v>
+        <v>2.855857721168332e-05</v>
       </c>
       <c r="D284" t="n">
         <v>1.784911075730207e-05</v>
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196378e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>8.008582220202488e-05</v>
+        <v>8.008582220202486e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>1.48996878515395e-05</v>
+        <v>1.489968785153952e-05</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11048,10 +11048,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C321" t="n">
-        <v>8.448800270361608e-05</v>
+        <v>8.448800270361609e-05</v>
       </c>
       <c r="D321" t="n">
-        <v>1.689760054072323e-05</v>
+        <v>1.689760054072321e-05</v>
       </c>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
@@ -11112,10 +11112,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C323" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D323" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11144,7 +11144,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D324" t="n">
         <v>2.206548516810006e-05</v>
@@ -11176,10 +11176,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D325" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291307e-05</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>3.781596022601338e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>1.26053200753378e-05</v>
+        <v>1.260532007533779e-05</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11243,7 +11243,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>6.7271328667238e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>1.462420188418216e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11371,7 +11371,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>3.530754034834828e-05</v>
+        <v>3.530754034834829e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>2.159304120477498e-05</v>
+        <v>2.159304120477497e-05</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13192,7 +13192,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>3.226547440311831e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D388" t="n">
         <v>2.24970280241926e-05</v>
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653713</v>
+        <v>0.0001539523278653714</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349952e-05</v>
+        <v>2.123480384349949e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001596599792992579</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560601e-06</v>
+        <v>5.505516527560628e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>4.862394242925217e-05</v>
+        <v>4.862394242925216e-05</v>
       </c>
       <c r="D422" t="n">
         <v>1.736569372473291e-05</v>
@@ -14355,7 +14355,7 @@
         <v>0.0002159069441070898</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011905e-05</v>
+        <v>6.072382803011902e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.30563090409638e-05</v>
+        <v>4.305630904096379e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001331164744948835</v>
       </c>
       <c r="D430" t="n">
-        <v>2.420299536270607e-05</v>
+        <v>2.42029953627061e-05</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14607,7 +14607,7 @@
         <v>0.0001756697408871322</v>
       </c>
       <c r="D437" t="n">
-        <v>3.293807641633728e-05</v>
+        <v>3.29380764163373e-05</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747833e-05</v>
+        <v>8.361934951747836e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408698e-05</v>
+        <v>1.520351809408696e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
         <v>2.731046537032991e-05</v>
       </c>
       <c r="C441" t="n">
-        <v>1.365523268516495e-05</v>
+        <v>1.365523268516496e-05</v>
       </c>
       <c r="D441" t="n">
         <v>1.365523268516495e-05</v>
@@ -14884,10 +14884,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C447" t="n">
-        <v>3.511729175445989e-05</v>
+        <v>3.51172917544599e-05</v>
       </c>
       <c r="D447" t="n">
-        <v>2.748309789479471e-05</v>
+        <v>2.74830978947947e-05</v>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C448" t="n">
-        <v>8.979401253524414e-05</v>
+        <v>8.979401253524415e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>3.142790438733547e-05</v>
+        <v>3.142790438733546e-05</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D454" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C463" t="n">
-        <v>8.742022904100011e-05</v>
+        <v>8.74202290410001e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>2.964686028346956e-05</v>
+        <v>2.964686028346958e-05</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15360,10 +15360,10 @@
         <v>3.051106025934401e-05</v>
       </c>
       <c r="C464" t="n">
-        <v>9.57209733626479e-06</v>
+        <v>9.572097336264788e-06</v>
       </c>
       <c r="D464" t="n">
-        <v>2.093896292307922e-05</v>
+        <v>2.093896292307923e-05</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15559,7 +15559,7 @@
         <v>2.74830978947947e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.832206526319647e-05</v>
+        <v>1.832206526319646e-05</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0001623358448741057</v>
       </c>
       <c r="D540" t="n">
-        <v>4.47823020342361e-05</v>
+        <v>4.478230203423613e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0008887760284408329</v>
+        <v>0.000888776028440833</v>
       </c>
       <c r="D547" t="n">
-        <v>2.539360081259528e-05</v>
+        <v>2.539360081259517e-05</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860081</v>
       </c>
       <c r="D548" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.735720922762802e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17740,10 +17740,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C549" t="n">
-        <v>0.0001318629153132403</v>
+        <v>0.0001318629153132404</v>
       </c>
       <c r="D549" t="n">
-        <v>4.615202035963416e-05</v>
+        <v>4.615202035963413e-05</v>
       </c>
       <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.47721690879077e-05</v>
+        <v>3.477216908790768e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
         <v>1.218034981964682e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>1.974056694908278e-05</v>
+        <v>1.974056694908277e-05</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18468,7 +18468,7 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>2.855857721168331e-05</v>
+        <v>2.855857721168332e-05</v>
       </c>
       <c r="D575" t="n">
         <v>1.784911075730207e-05</v>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196378e-05</v>
+        <v>2.263253406196376e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>8.008582220202488e-05</v>
+        <v>8.008582220202486e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>1.48996878515395e-05</v>
+        <v>1.489968785153952e-05</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241925</v>
+        <v>0.0007840209072241928</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429729e-05</v>
+        <v>4.666791114429707e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>1.92785536800617e-05</v>
+        <v>1.927855368006169e-05</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21772,10 +21772,10 @@
         <v>0.0001013856032443393</v>
       </c>
       <c r="C693" t="n">
-        <v>8.448800270361608e-05</v>
+        <v>8.448800270361609e-05</v>
       </c>
       <c r="D693" t="n">
-        <v>1.689760054072323e-05</v>
+        <v>1.689760054072321e-05</v>
       </c>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="inlineStr"/>
@@ -21996,10 +21996,10 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="C701" t="n">
-        <v>8.22451838591085e-05</v>
+        <v>8.224518385910852e-05</v>
       </c>
       <c r="D701" t="n">
-        <v>2.467355515773257e-05</v>
+        <v>2.467355515773255e-05</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22024,7 +22024,7 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>4.932284919928248e-05</v>
+        <v>4.932284919928247e-05</v>
       </c>
       <c r="D702" t="n">
         <v>2.206548516810006e-05</v>
@@ -22052,10 +22052,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0001068677816538552</v>
+        <v>0.0001068677816538553</v>
       </c>
       <c r="D703" t="n">
-        <v>1.145011946291308e-05</v>
+        <v>1.145011946291307e-05</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22248,10 +22248,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>3.781596022601338e-05</v>
+        <v>3.781596022601339e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>1.26053200753378e-05</v>
+        <v>1.260532007533779e-05</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22279,7 +22279,7 @@
         <v>2.188268691544629e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>1.492001380598611e-05</v>
+        <v>1.492001380598612e-05</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>6.7271328667238e-05</v>
+        <v>6.727132866723798e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>1.462420188418216e-05</v>
+        <v>1.462420188418217e-05</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>3.530754034834828e-05</v>
+        <v>3.530754034834829e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>2.159304120477498e-05</v>
+        <v>2.159304120477497e-05</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22556,7 +22556,7 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>3.226547440311831e-05</v>
+        <v>3.226547440311832e-05</v>
       </c>
       <c r="D721" t="n">
         <v>2.24970280241926e-05</v>
@@ -22892,10 +22892,10 @@
         <v>3.766524531461867e-05</v>
       </c>
       <c r="C733" t="n">
-        <v>2.715401406402742e-05</v>
+        <v>2.715401406402741e-05</v>
       </c>
       <c r="D733" t="n">
-        <v>1.051123125059125e-05</v>
+        <v>1.051123125059126e-05</v>
       </c>
       <c r="E733" t="inlineStr"/>
       <c r="F733" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500522e-05</v>
+        <v>2.700608818500524e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23315,7 +23315,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1524,10 +1524,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C31" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.0001294575727700933</v>
       </c>
       <c r="D35" t="n">
-        <v>5.726008026369514e-05</v>
+        <v>5.726008026369511e-05</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D37" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>4.854958125986163e-05</v>
+        <v>4.854958125986164e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482698e-06</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D71" t="n">
         <v>1.260532007533779e-05</v>
@@ -3000,10 +3000,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D75" t="n">
-        <v>1.488974146445571e-05</v>
+        <v>1.488974146445572e-05</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>3.530754034834829e-05</v>
+        <v>3.530754034834827e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>2.159304120477497e-05</v>
+        <v>2.159304120477499e-05</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C97" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>0.0001294575727700933</v>
       </c>
       <c r="D107" t="n">
-        <v>5.726008026369514e-05</v>
+        <v>5.726008026369511e-05</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D112" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>4.854958125986163e-05</v>
+        <v>4.854958125986164e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482698e-06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D175" t="n">
-        <v>1.838566150642433e-05</v>
+        <v>1.838566150642434e-05</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D188" t="n">
         <v>1.260532007533779e-05</v>
@@ -6824,10 +6824,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>3.530754034834829e-05</v>
+        <v>3.530754034834827e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>2.159304120477497e-05</v>
+        <v>2.159304120477499e-05</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>3.567852498072209e-05</v>
       </c>
       <c r="C198" t="n">
-        <v>2.301840321336909e-05</v>
+        <v>2.301840321336908e-05</v>
       </c>
       <c r="D198" t="n">
         <v>1.2660121767353e-05</v>
@@ -7979,7 +7979,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D225" t="n">
-        <v>1.488974146445571e-05</v>
+        <v>1.488974146445572e-05</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8168,10 +8168,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0001596599792992579</v>
+        <v>0.0001596599792992578</v>
       </c>
       <c r="D231" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560655e-06</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8328,10 +8328,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0003835999729223549</v>
+        <v>0.0003835999729223548</v>
       </c>
       <c r="D236" t="n">
-        <v>2.256470428955027e-05</v>
+        <v>2.256470428955033e-05</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8488,10 +8488,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C241" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D241" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747833e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.520351809408698e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>6.127332417458383e-05</v>
+        <v>6.127332417458382e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>1.934947079197383e-05</v>
+        <v>1.934947079197384e-05</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8872,10 +8872,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C253" t="n">
-        <v>8.979401253524415e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D253" t="n">
-        <v>3.142790438733546e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8907,7 +8907,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D254" t="n">
-        <v>6.747092003346557e-05</v>
+        <v>6.747092003346559e-05</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0002526792715866515</v>
+        <v>0.0002526792715866516</v>
       </c>
       <c r="D256" t="n">
-        <v>6.002342849951113e-05</v>
+        <v>6.002342849951108e-05</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306984e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9160,10 +9160,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C262" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100009e-05</v>
       </c>
       <c r="D262" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346959e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9192,7 +9192,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>4.256883574234245e-05</v>
+        <v>4.256883574234244e-05</v>
       </c>
       <c r="D263" t="n">
         <v>2.321936495036861e-05</v>
@@ -9256,10 +9256,10 @@
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C265" t="n">
-        <v>5.028464701973673e-05</v>
+        <v>5.028464701973672e-05</v>
       </c>
       <c r="D265" t="n">
-        <v>1.257116175493417e-05</v>
+        <v>1.257116175493418e-05</v>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
@@ -9291,7 +9291,7 @@
         <v>0.0001294575727700933</v>
       </c>
       <c r="D266" t="n">
-        <v>5.726008026369514e-05</v>
+        <v>5.726008026369511e-05</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D271" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860081</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D272" t="n">
-        <v>5.735720922762802e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D277" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D292" t="n">
-        <v>1.970896947317137e-05</v>
+        <v>1.970896947317136e-05</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10187,7 +10187,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C319" t="n">
-        <v>4.854958125986163e-05</v>
+        <v>4.854958125986164e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482698e-06</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11208,7 +11208,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D326" t="n">
         <v>1.260532007533779e-05</v>
@@ -11240,10 +11240,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D330" t="n">
-        <v>1.488974146445571e-05</v>
+        <v>1.488974146445572e-05</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11371,7 +11371,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>3.530754034834829e-05</v>
+        <v>3.530754034834827e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>2.159304120477497e-05</v>
+        <v>2.159304120477499e-05</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13708,10 +13708,10 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0001596599792992579</v>
+        <v>0.0001596599792992578</v>
       </c>
       <c r="D405" t="n">
-        <v>5.505516527560628e-06</v>
+        <v>5.505516527560655e-06</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0003835999729223549</v>
+        <v>0.0003835999729223548</v>
       </c>
       <c r="D413" t="n">
-        <v>2.256470428955027e-05</v>
+        <v>2.256470428955033e-05</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14240,10 +14240,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C424" t="n">
-        <v>8.868351653480828e-05</v>
+        <v>8.868351653480827e-05</v>
       </c>
       <c r="D424" t="n">
-        <v>3.50066512637401e-05</v>
+        <v>3.500665126374012e-05</v>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747836e-05</v>
+        <v>8.361934951747833e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408696e-05</v>
+        <v>1.520351809408698e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>6.127332417458383e-05</v>
+        <v>6.127332417458382e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>1.934947079197383e-05</v>
+        <v>1.934947079197384e-05</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="C448" t="n">
-        <v>8.979401253524415e-05</v>
+        <v>8.979401253524414e-05</v>
       </c>
       <c r="D448" t="n">
-        <v>3.142790438733546e-05</v>
+        <v>3.142790438733547e-05</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15027,7 +15027,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D452" t="n">
-        <v>6.747092003346557e-05</v>
+        <v>6.747092003346559e-05</v>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0002526792715866515</v>
+        <v>0.0002526792715866516</v>
       </c>
       <c r="D454" t="n">
-        <v>6.002342849951113e-05</v>
+        <v>6.002342849951108e-05</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306983e-05</v>
+        <v>2.635046113306984e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15332,10 +15332,10 @@
         <v>0.0001170670893244697</v>
       </c>
       <c r="C463" t="n">
-        <v>8.74202290410001e-05</v>
+        <v>8.742022904100009e-05</v>
       </c>
       <c r="D463" t="n">
-        <v>2.964686028346958e-05</v>
+        <v>2.964686028346959e-05</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15416,7 +15416,7 @@
         <v>4.188920305791183e-05</v>
       </c>
       <c r="C466" t="n">
-        <v>1.730206213261575e-05</v>
+        <v>1.730206213261576e-05</v>
       </c>
       <c r="D466" t="n">
         <v>2.458714092529607e-05</v>
@@ -15528,7 +15528,7 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>4.256883574234245e-05</v>
+        <v>4.256883574234244e-05</v>
       </c>
       <c r="D470" t="n">
         <v>2.321936495036861e-05</v>
@@ -15584,10 +15584,10 @@
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C472" t="n">
-        <v>5.028464701973673e-05</v>
+        <v>5.028464701973672e-05</v>
       </c>
       <c r="D472" t="n">
-        <v>1.257116175493417e-05</v>
+        <v>1.257116175493418e-05</v>
       </c>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
@@ -17463,7 +17463,7 @@
         <v>0.0001294575727700933</v>
       </c>
       <c r="D539" t="n">
-        <v>5.726008026369514e-05</v>
+        <v>5.726008026369511e-05</v>
       </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.000888776028440833</v>
+        <v>0.0008887760284408329</v>
       </c>
       <c r="D547" t="n">
-        <v>2.539360081259517e-05</v>
+        <v>2.539360081259528e-05</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860081</v>
+        <v>0.0006768150688860082</v>
       </c>
       <c r="D548" t="n">
-        <v>5.735720922762802e-05</v>
+        <v>5.735720922762791e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D559" t="n">
-        <v>3.482901632141288e-05</v>
+        <v>3.482901632141286e-05</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.664680778255083e-05</v>
+        <v>2.66468077825508e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
         <v>1.218034981964682e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>1.974056694908277e-05</v>
+        <v>1.974056694908278e-05</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18779,7 +18779,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D586" t="n">
-        <v>1.970896947317137e-05</v>
+        <v>1.970896947317136e-05</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880435e-05</v>
+        <v>1.872904687880434e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19003,7 +19003,7 @@
         <v>3.420241241015532e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507767e-05</v>
+        <v>1.710120620507768e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21716,10 +21716,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C691" t="n">
-        <v>4.854958125986163e-05</v>
+        <v>4.854958125986164e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>6.068697657482705e-06</v>
+        <v>6.068697657482698e-06</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457079e-06</v>
+        <v>5.746465923457075e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21887,7 +21887,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D697" t="n">
-        <v>1.838566150642433e-05</v>
+        <v>1.838566150642434e-05</v>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr"/>
@@ -22248,7 +22248,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>3.781596022601339e-05</v>
+        <v>3.78159602260134e-05</v>
       </c>
       <c r="D710" t="n">
         <v>1.260532007533779e-05</v>
@@ -22276,10 +22276,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>2.188268691544629e-05</v>
+        <v>2.18826869154463e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>1.492001380598612e-05</v>
+        <v>1.492001380598611e-05</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392302e-05</v>
+        <v>3.617156992392301e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.944708060425969e-05</v>
+        <v>1.94470806042597e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>3.530754034834829e-05</v>
+        <v>3.530754034834827e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>2.159304120477497e-05</v>
+        <v>2.159304120477499e-05</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22528,7 +22528,7 @@
         <v>3.567852498072209e-05</v>
       </c>
       <c r="C720" t="n">
-        <v>2.301840321336909e-05</v>
+        <v>2.301840321336908e-05</v>
       </c>
       <c r="D720" t="n">
         <v>1.2660121767353e-05</v>
@@ -23287,7 +23287,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D747" t="n">
-        <v>1.488974146445571e-05</v>
+        <v>1.488974146445572e-05</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23315,7 +23315,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>1.644899167681022e-05</v>
+        <v>1.644899167681021e-05</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_vgene_decomposition_CDR3b.xlsx
@@ -1488,10 +1488,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D30" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349954e-05</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C31" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D36" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D37" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D62" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>4.854958125986164e-05</v>
+        <v>4.854958125986163e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>6.068697657482698e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D67" t="n">
-        <v>3.069580937579264e-05</v>
+        <v>3.069580937579263e-05</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D70" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D72" t="n">
         <v>1.492001380598611e-05</v>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.727132866723797e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418218e-05</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D74" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D75" t="n">
-        <v>1.488974146445572e-05</v>
+        <v>1.48897414644557e-05</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392303e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425968e-05</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D93" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349954e-05</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C97" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D97" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4136,10 +4136,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C105" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D108" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D112" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D161" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>1.927855368006169e-05</v>
+        <v>1.92785536800617e-05</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>4.854958125986164e-05</v>
+        <v>4.854958125986163e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>6.068697657482698e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D172" t="n">
-        <v>3.069580937579264e-05</v>
+        <v>3.069580937579263e-05</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D175" t="n">
-        <v>1.838566150642434e-05</v>
+        <v>1.838566150642433e-05</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D181" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D189" t="n">
         <v>1.492001380598611e-05</v>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.727132866723797e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418218e-05</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392303e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425968e-05</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>3.567852498072209e-05</v>
       </c>
       <c r="C198" t="n">
-        <v>2.301840321336908e-05</v>
+        <v>2.301840321336909e-05</v>
       </c>
       <c r="D198" t="n">
         <v>1.2660121767353e-05</v>
@@ -7336,10 +7336,10 @@
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C205" t="n">
-        <v>3.385888550559488e-05</v>
+        <v>3.385888550559489e-05</v>
       </c>
       <c r="D205" t="n">
-        <v>1.167547776055002e-06</v>
+        <v>1.167547776054995e-06</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D224" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D225" t="n">
-        <v>1.488974146445572e-05</v>
+        <v>1.48897414644557e-05</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D228" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349954e-05</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>0.000112632465573642</v>
       </c>
       <c r="D230" t="n">
-        <v>3.427944604415193e-05</v>
+        <v>3.427944604415195e-05</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8488,10 +8488,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C241" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D241" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8520,10 +8520,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0002159069441070898</v>
+        <v>0.0002159069441070899</v>
       </c>
       <c r="D242" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011899e-05</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D243" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.305630904096377e-05</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>8.361934951747833e-05</v>
+        <v>8.361934951747834e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>1.520351809408698e-05</v>
+        <v>1.520351809408697e-05</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8840,10 +8840,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C252" t="n">
-        <v>3.51172917544599e-05</v>
+        <v>3.511729175445989e-05</v>
       </c>
       <c r="D252" t="n">
-        <v>2.74830978947947e-05</v>
+        <v>2.748309789479471e-05</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8907,7 +8907,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D254" t="n">
-        <v>6.747092003346559e-05</v>
+        <v>6.747092003346557e-05</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8936,10 +8936,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C255" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D255" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D256" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9099,7 +9099,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D260" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D261" t="n">
-        <v>3.57110972234622e-05</v>
+        <v>3.571109722346218e-05</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9320,10 +9320,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D267" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860084</v>
       </c>
       <c r="D272" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.73572092276277e-05</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9512,10 +9512,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0001318629153132404</v>
+        <v>0.0001318629153132403</v>
       </c>
       <c r="D273" t="n">
-        <v>4.615202035963413e-05</v>
+        <v>4.615202035963416e-05</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9544,10 +9544,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C274" t="n">
-        <v>5.96698764087685e-05</v>
+        <v>5.966987640876849e-05</v>
       </c>
       <c r="D274" t="n">
-        <v>1.491746910219211e-05</v>
+        <v>1.491746910219212e-05</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D277" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9803,7 +9803,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D282" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D283" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D290" t="n">
-        <v>4.099107305520131e-05</v>
+        <v>4.099107305520128e-05</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -10091,7 +10091,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D291" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D292" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10155,7 +10155,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>3.420241241015532e-05</v>
+        <v>3.420241241015533e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507766e-05</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>8.008582220202486e-05</v>
+        <v>8.008582220202488e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>1.489968785153952e-05</v>
+        <v>1.48996878515395e-05</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D317" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C319" t="n">
-        <v>4.854958125986164e-05</v>
+        <v>4.854958125986163e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>6.068697657482698e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D322" t="n">
-        <v>3.069580937579264e-05</v>
+        <v>3.069580937579263e-05</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11176,10 +11176,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D325" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11240,7 +11240,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D327" t="n">
         <v>1.492001380598611e-05</v>
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.727132866723797e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418218e-05</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D329" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D330" t="n">
-        <v>1.488974146445572e-05</v>
+        <v>1.48897414644557e-05</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11371,7 +11371,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -11432,10 +11432,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C333" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392303e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425968e-05</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13540,10 +13540,10 @@
         <v>0.0001751871317088708</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0001539523278653714</v>
+        <v>0.0001539523278653713</v>
       </c>
       <c r="D399" t="n">
-        <v>2.123480384349949e-05</v>
+        <v>2.123480384349954e-05</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13683,7 +13683,7 @@
         <v>0.000112632465573642</v>
       </c>
       <c r="D404" t="n">
-        <v>3.427944604415193e-05</v>
+        <v>3.427944604415195e-05</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -14215,7 +14215,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D423" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
@@ -14240,10 +14240,10 @@
         <v>0.0001236901677985484</v>
       </c>
       <c r="C424" t="n">
-        <v>8.868351653480827e-05</v>
+        <v>8.868351653480828e-05</v>
       </c>
       <c r="D424" t="n">
-        <v>3.500665126374012e-05</v>
+        <v>3.50066512637401e-05</v>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002159069441070898</v>
+        <v>0.0002159069441070899</v>
       </c>
       <c r="D428" t="n">
-        <v>6.072382803011902e-05</v>
+        <v>6.072382803011899e-05</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001097935880544576</v>
       </c>
       <c r="D429" t="n">
-        <v>4.305630904096379e-05</v>
+        <v>4.305630904096377e-05</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>8.361934951747833e-05</v>
+        <v>8.361934951747834e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>1.520351809408698e-05</v>
+        <v>1.520351809408697e-05</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14884,10 +14884,10 @@
         <v>6.26003896492546e-05</v>
       </c>
       <c r="C447" t="n">
-        <v>3.51172917544599e-05</v>
+        <v>3.511729175445989e-05</v>
       </c>
       <c r="D447" t="n">
-        <v>2.74830978947947e-05</v>
+        <v>2.748309789479471e-05</v>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr"/>
@@ -15027,7 +15027,7 @@
         <v>0.0001565325344776401</v>
       </c>
       <c r="D452" t="n">
-        <v>6.747092003346559e-05</v>
+        <v>6.747092003346557e-05</v>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
@@ -15052,10 +15052,10 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="C453" t="n">
-        <v>8.611261808192752e-05</v>
+        <v>8.611261808192754e-05</v>
       </c>
       <c r="D453" t="n">
-        <v>3.616729959440959e-05</v>
+        <v>3.616729959440958e-05</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0002526792715866516</v>
+        <v>0.0002526792715866515</v>
       </c>
       <c r="D454" t="n">
-        <v>6.002342849951108e-05</v>
+        <v>6.002342849951113e-05</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
         <v>0.0001185770750988142</v>
       </c>
       <c r="D461" t="n">
-        <v>2.635046113306984e-05</v>
+        <v>2.635046113306983e-05</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15307,7 +15307,7 @@
         <v>0.0001448283387395967</v>
       </c>
       <c r="D462" t="n">
-        <v>3.57110972234622e-05</v>
+        <v>3.571109722346218e-05</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15416,7 +15416,7 @@
         <v>4.188920305791183e-05</v>
       </c>
       <c r="C466" t="n">
-        <v>1.730206213261576e-05</v>
+        <v>1.730206213261575e-05</v>
       </c>
       <c r="D466" t="n">
         <v>2.458714092529607e-05</v>
@@ -15640,10 +15640,10 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="C474" t="n">
-        <v>0.001690140845070423</v>
+        <v>0.001690140845070422</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17488,10 +17488,10 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="C540" t="n">
-        <v>0.0001623358448741057</v>
+        <v>0.0001623358448741058</v>
       </c>
       <c r="D540" t="n">
-        <v>4.478230203423613e-05</v>
+        <v>4.478230203423607e-05</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0006768150688860082</v>
+        <v>0.0006768150688860084</v>
       </c>
       <c r="D548" t="n">
-        <v>5.735720922762791e-05</v>
+        <v>5.73572092276277e-05</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17740,10 +17740,10 @@
         <v>0.0001780149356728745</v>
       </c>
       <c r="C549" t="n">
-        <v>0.0001318629153132404</v>
+        <v>0.0001318629153132403</v>
       </c>
       <c r="D549" t="n">
-        <v>4.615202035963413e-05</v>
+        <v>4.615202035963416e-05</v>
       </c>
       <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr"/>
@@ -17768,7 +17768,7 @@
         <v>4.151028244288012e-05</v>
       </c>
       <c r="C550" t="n">
-        <v>1.556635591608004e-05</v>
+        <v>1.556635591608005e-05</v>
       </c>
       <c r="D550" t="n">
         <v>2.594392652680007e-05</v>
@@ -17936,10 +17936,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C556" t="n">
-        <v>5.96698764087685e-05</v>
+        <v>5.966987640876849e-05</v>
       </c>
       <c r="D556" t="n">
-        <v>1.491746910219211e-05</v>
+        <v>1.491746910219212e-05</v>
       </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001035939972636896</v>
       </c>
       <c r="D559" t="n">
-        <v>3.482901632141286e-05</v>
+        <v>3.482901632141288e-05</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
         <v>0.0001207875347264162</v>
       </c>
       <c r="D567" t="n">
-        <v>3.477216908790768e-05</v>
+        <v>3.47721690879077e-05</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001472586745877809</v>
       </c>
       <c r="D568" t="n">
-        <v>2.66468077825508e-05</v>
+        <v>2.664680778255083e-05</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18723,7 +18723,7 @@
         <v>0.0001366369101840044</v>
       </c>
       <c r="D584" t="n">
-        <v>4.099107305520131e-05</v>
+        <v>4.099107305520128e-05</v>
       </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
         <v>0.000166657750819915</v>
       </c>
       <c r="D585" t="n">
-        <v>2.263253406196376e-05</v>
+        <v>2.263253406196378e-05</v>
       </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr"/>
@@ -18779,7 +18779,7 @@
         <v>0.0001056400763761985</v>
       </c>
       <c r="D586" t="n">
-        <v>1.970896947317136e-05</v>
+        <v>1.970896947317137e-05</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18975,7 +18975,7 @@
         <v>4.949819532255431e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.872904687880434e-05</v>
+        <v>1.872904687880435e-05</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>3.420241241015532e-05</v>
+        <v>3.420241241015533e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.710120620507768e-05</v>
+        <v>1.710120620507766e-05</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>8.008582220202486e-05</v>
+        <v>8.008582220202488e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>1.489968785153952e-05</v>
+        <v>1.48996878515395e-05</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0007840209072241928</v>
+        <v>0.0007840209072241927</v>
       </c>
       <c r="D683" t="n">
-        <v>4.666791114429707e-05</v>
+        <v>4.666791114429718e-05</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>1.927855368006169e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>1.927855368006169e-05</v>
+        <v>1.92785536800617e-05</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21716,10 +21716,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C691" t="n">
-        <v>4.854958125986164e-05</v>
+        <v>4.854958125986163e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>6.068697657482698e-06</v>
+        <v>6.068697657482705e-06</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.298586369382829e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>5.746465923457075e-06</v>
+        <v>5.746465923457079e-06</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001114742551015627</v>
       </c>
       <c r="D694" t="n">
-        <v>3.069580937579264e-05</v>
+        <v>3.069580937579263e-05</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21887,7 +21887,7 @@
         <v>2.322399348179916e-05</v>
       </c>
       <c r="D697" t="n">
-        <v>1.838566150642434e-05</v>
+        <v>1.838566150642433e-05</v>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr"/>
@@ -22052,10 +22052,10 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0001068677816538553</v>
+        <v>0.0001068677816538552</v>
       </c>
       <c r="D703" t="n">
-        <v>1.145011946291307e-05</v>
+        <v>1.145011946291308e-05</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22276,7 +22276,7 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>2.18826869154463e-05</v>
+        <v>2.188268691544629e-05</v>
       </c>
       <c r="D711" t="n">
         <v>1.492001380598611e-05</v>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>6.727132866723798e-05</v>
+        <v>6.727132866723797e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>1.462420188418217e-05</v>
+        <v>1.462420188418218e-05</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>3.617156992392301e-05</v>
+        <v>3.617156992392303e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>1.94470806042597e-05</v>
+        <v>1.944708060425968e-05</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>3.530754034834827e-05</v>
+        <v>3.530754034834828e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>2.159304120477499e-05</v>
+        <v>2.159304120477498e-05</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22528,7 +22528,7 @@
         <v>3.567852498072209e-05</v>
       </c>
       <c r="C720" t="n">
-        <v>2.301840321336908e-05</v>
+        <v>2.301840321336909e-05</v>
       </c>
       <c r="D720" t="n">
         <v>1.2660121767353e-05</v>
@@ -22724,10 +22724,10 @@
         <v>3.502643328164988e-05</v>
       </c>
       <c r="C727" t="n">
-        <v>3.385888550559488e-05</v>
+        <v>3.385888550559489e-05</v>
       </c>
       <c r="D727" t="n">
-        <v>1.167547776055002e-06</v>
+        <v>1.167547776054995e-06</v>
       </c>
       <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001282789188787747</v>
       </c>
       <c r="D746" t="n">
-        <v>2.700608818500524e-05</v>
+        <v>2.700608818500522e-05</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
         <v>0.0001116730609834178</v>
       </c>
       <c r="D747" t="n">
-        <v>1.488974146445572e-05</v>
+        <v>1.48897414644557e-05</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23315,7 +23315,7 @@
         <v>3.87726232381955e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>1.644899167681021e-05</v>
+        <v>1.644899167681022e-05</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>
